--- a/Projeto DIO.xlsx
+++ b/Projeto DIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theoe\Desktop\Planilhas de Prática DIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF6F5C8-D14B-4770-A0FA-14BA3C8C1119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D96B0B-8E75-4C89-9DB3-45B0850F5E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="10" xr2:uid="{8F1A8072-ACDE-4D80-9C15-DAEAF7D32DC8}"/>
   </bookViews>
@@ -154,9 +154,9 @@
   <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.000;[Red]\-&quot;R$&quot;\ #,##0.000"/>
-    <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.000;[Red]\-&quot;R$&quot;\ #,##0.000"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -672,19 +672,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -702,13 +702,13 @@
     <xf numFmtId="8" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -720,7 +720,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -732,13 +732,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,28 +747,34 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -789,14 +795,32 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -816,12 +840,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -830,24 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -867,6 +867,828 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Simulador!$C$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Percentual Sugerido</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent6">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-AC12-46EB-85F9-555FBC0FEBE7}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-AC12-46EB-85F9-555FBC0FEBE7}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-AC12-46EB-85F9-555FBC0FEBE7}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Simulador!$B$27:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Papel</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tijolo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Hibridos</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Simulador!$C$27:$C$29</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5046-40BA-A4C0-5E6A7556B783}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="255">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>341982</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>11476</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>378704</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>51872</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F11A5F-0752-DB52-EF01-A7FD79810D88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1186,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E85C95B-F577-4E20-8AFA-F760816A8253}">
-  <dimension ref="A2:F54"/>
+  <dimension ref="A2:G57"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -1201,35 +2023,35 @@
   <sheetData>
     <row r="2" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:5" ht="30.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
     </row>
     <row r="4" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="39"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="15">
         <v>7000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="41"/>
+      <c r="C5" s="43"/>
       <c r="D5" s="16">
         <v>1.01E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="43"/>
+      <c r="C6" s="45"/>
       <c r="D6" s="17">
         <f>salario*28%</f>
         <v>1960.0000000000002</v>
@@ -1239,55 +2061,55 @@
       <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="60"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="54"/>
     </row>
     <row r="9" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="48"/>
+      <c r="C9" s="56"/>
       <c r="D9" s="5">
         <f>sug_invest</f>
         <v>1960.0000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="50"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="50"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="7">
         <v>1.01E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="52"/>
+      <c r="C12" s="60"/>
       <c r="D12" s="8">
         <f>FV(Tx_mensal,periodo*12,Aporte*-1)</f>
         <v>52930.727155175009</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="54"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="9">
         <f>patrimonio*Rendimento_carteira</f>
         <v>534.60034426726759</v>
@@ -1295,13 +2117,13 @@
     </row>
     <row r="14" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:5" ht="30.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1309,7 +2131,7 @@
       <c r="A16" s="4">
         <v>2</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="34" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="10">
@@ -1325,7 +2147,7 @@
       <c r="A17" s="4">
         <v>7</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="35" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="12">
@@ -1341,7 +2163,7 @@
       <c r="A18" s="4">
         <v>10</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="35" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="12">
@@ -1357,7 +2179,7 @@
       <c r="A19" s="4">
         <v>20</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="12">
@@ -1373,7 +2195,7 @@
       <c r="A20" s="4">
         <v>30</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="36" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="13">
@@ -1390,20 +2212,20 @@
       <c r="B23" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="34"/>
+      <c r="C23" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="47"/>
     </row>
     <row r="24" spans="1:4" ht="25.5" x14ac:dyDescent="0.5">
       <c r="B24" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="48">
         <f>Aporte</f>
         <v>1960.0000000000002</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="49"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
@@ -1427,11 +2249,11 @@
       </c>
       <c r="C27" s="29">
         <f>VLOOKUP($C$23&amp;"-"&amp;B27,PROV!$A$2:$D$13,4,FALSE)</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D27" s="30">
         <f>C27*$C$24</f>
-        <v>686</v>
+        <v>196.00000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
@@ -1440,11 +2262,11 @@
       </c>
       <c r="C28" s="29">
         <f>VLOOKUP($C$23&amp;"-"&amp;B28,PROV!$A$2:$D$13,4,FALSE)</f>
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="30">
         <f t="shared" ref="D28:D29" si="0">C28*$C$24</f>
-        <v>490.00000000000006</v>
+        <v>1568.0000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
@@ -1453,24 +2275,24 @@
       </c>
       <c r="C29" s="29">
         <f>VLOOKUP($C$23&amp;"-"&amp;B29,PROV!$A$2:$D$13,4,FALSE)</f>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D29" s="30">
         <f t="shared" si="0"/>
-        <v>784.00000000000011</v>
+        <v>196.00000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="33">
         <f>SUM(C27,C28,C29)</f>
         <v>1</v>
       </c>
       <c r="D30" s="32">
         <f>SUM(D27:D29)</f>
-        <v>1960</v>
+        <v>1960.0000000000002</v>
       </c>
     </row>
     <row r="33" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -1495,8 +2317,12 @@
     <row r="52" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="53" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="54" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
@@ -1508,7 +2334,6 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B3:D3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Coloque um perfil adequado " sqref="C23" xr:uid="{773B65FD-287C-4542-8967-B0A37D913E73}">
@@ -1516,6 +2341,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
